--- a/data/THC Daily Buying Brief.xlsx
+++ b/data/THC Daily Buying Brief.xlsx
@@ -464,7 +464,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>* 1060 stockouts on sellers | 918 fixable by transfer | 655 need a buy</t>
+          <t>* 1060 stockouts on sellers | 917 fixable by transfer | 655 need a buy</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Transfer 1 from Rosemount</t>
+          <t>Transfer 1 from Chanhassen</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Transfer 10 from Rosemount</t>
+          <t>Transfer 10 from Andover</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Transfer 12 from Andover</t>
+          <t>Transfer 12 from Rosemount</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Transfer 1 from Stillwater</t>
+          <t>Transfer 1 from Plymouth</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Transfer 21 from Rosemount</t>
+          <t>Transfer 21 from Andover</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Transfer 3 from Plymouth</t>
+          <t>Transfer 3 from Stillwater</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Transfer 10 from Chanhassen</t>
+          <t>Transfer 10 from Rosemount</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Transfer 5 from Andover</t>
+          <t>Transfer 5 from Rosemount</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Transfer 7 from Vadnais Heights, 3 from Osseo</t>
+          <t>Transfer 7 from Osseo, 3 from Vadnais Heights</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Transfer 2 from Roseville, 2 from Woodbury, 2 from Rosemount</t>
+          <t>Transfer 2 from Rosemount, 2 from Roseville, 2 from St. Louis Park</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Transfer 3 from Vadnais Heights</t>
+          <t>Transfer 3 from Stillwater</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Transfer 2 from Ramsey</t>
+          <t>Transfer 2 from Blaine</t>
         </is>
       </c>
     </row>
@@ -12223,25 +12223,20 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E281" t="n">
         <v>1.9</v>
       </c>
       <c r="F281" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G281" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12254,7 +12249,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Transfer 6 from Chanhassen</t>
+          <t>Transfer 5 from Chanhassen</t>
         </is>
       </c>
     </row>
@@ -12266,20 +12261,25 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Vadnais Heights</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E282" t="n">
         <v>1.9</v>
       </c>
       <c r="F282" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G282" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12292,7 +12292,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Transfer 5 from Bloomington</t>
+          <t>Transfer 6 from Bloomington</t>
         </is>
       </c>
     </row>
@@ -13097,7 +13097,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Transfer 2 from Minnetonka</t>
+          <t>Transfer 2 from Andover</t>
         </is>
       </c>
     </row>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="D315" t="n">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="D316" t="n">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Transfer 4 from Minnetonka, 1 from Ramsey</t>
+          <t>Transfer 4 from Minnetonka, 1 from Andover</t>
         </is>
       </c>
     </row>
@@ -14927,7 +14927,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Transfer 1 from Minnetonka, 1 from Bloomington</t>
+          <t>Transfer 1 from Bloomington, 1 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Transfer 6 from Cottage Grove</t>
+          <t>Transfer 6 from Chanhassen</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Transfer 5 from Ramsey</t>
+          <t>Transfer 5 from Osseo</t>
         </is>
       </c>
     </row>
@@ -15435,20 +15435,20 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E360" t="n">
         <v>1.3</v>
       </c>
       <c r="F360" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Transfer 3 from Andover</t>
+          <t>Transfer 1 from Andover</t>
         </is>
       </c>
     </row>
@@ -15476,20 +15476,20 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E361" t="n">
         <v>1.3</v>
       </c>
       <c r="F361" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G361" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15505,7 +15505,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Transfer 1 from Andover</t>
+          <t>Transfer 3 from Andover</t>
         </is>
       </c>
     </row>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Transfer 3 from Ramsey, 2 from Minnetonka</t>
+          <t>Transfer 3 from Chanhassen, 2 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -16555,7 +16555,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Transfer 2 from Rosemount</t>
+          <t>Transfer 2 from Andover</t>
         </is>
       </c>
     </row>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Transfer 3 from Rosemount</t>
+          <t>Transfer 3 from Blaine</t>
         </is>
       </c>
     </row>
@@ -17404,7 +17404,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Transfer 1 from Rosemount, 1 from Andover; BUY 2</t>
+          <t>Transfer 1 from Ramsey, 1 from Rosemount; BUY 2</t>
         </is>
       </c>
     </row>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Transfer 1 from Minneapolis</t>
+          <t>Transfer 1 from Cottage Grove</t>
         </is>
       </c>
     </row>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="D449" t="n">
@@ -19136,7 +19136,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Transfer 1 from Andover</t>
+          <t>Transfer 1 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="D451" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Transfer 3 from Stillwater</t>
+          <t>Transfer 3 from Andover</t>
         </is>
       </c>
     </row>
@@ -19898,25 +19898,20 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Woodbury</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E467" t="n">
         <v>1</v>
       </c>
       <c r="F467" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G467" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -19929,7 +19924,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Transfer 4 from Blaine</t>
+          <t>Transfer 1 from Blaine</t>
         </is>
       </c>
     </row>
@@ -19941,20 +19936,25 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Woodbury</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E468" t="n">
         <v>1</v>
       </c>
       <c r="F468" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G468" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Transfer 1 from Blaine</t>
+          <t>Transfer 4 from Blaine</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Transfer 1 from Minneapolis</t>
+          <t>Transfer 1 from Cottage Grove</t>
         </is>
       </c>
     </row>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Transfer 3 from Cottage Grove</t>
+          <t>Transfer 3 from Minneapolis</t>
         </is>
       </c>
     </row>
@@ -20373,7 +20373,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Transfer 1 from Bloomington</t>
+          <t>Transfer 1 from Blaine</t>
         </is>
       </c>
     </row>
@@ -20492,7 +20492,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Transfer 1 from Andover</t>
+          <t>Transfer 1 from Minneapolis</t>
         </is>
       </c>
     </row>
@@ -20555,7 +20555,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Transfer 1 from Minneapolis</t>
+          <t>Transfer 1 from Andover</t>
         </is>
       </c>
     </row>
@@ -20696,7 +20696,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Transfer 4 from Osseo</t>
+          <t>Transfer 4 from Ramsey</t>
         </is>
       </c>
     </row>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -21729,7 +21729,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -21815,7 +21815,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t>Transfer 3 from Osseo</t>
+          <t>Transfer 3 from Vadnais Heights</t>
         </is>
       </c>
     </row>
@@ -22067,7 +22067,7 @@
       </c>
       <c r="M520" t="inlineStr">
         <is>
-          <t>Transfer 1 from St. Louis Park</t>
+          <t>Transfer 1 from Blaine</t>
         </is>
       </c>
     </row>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -22345,7 +22345,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -22459,7 +22459,7 @@
       </c>
       <c r="M529" t="inlineStr">
         <is>
-          <t>Transfer 3 from Chanhassen</t>
+          <t>Transfer 3 from Ramsey</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="M531" t="inlineStr">
         <is>
-          <t>Transfer 1 from Minnetonka, 1 from Roseville, 1 from Bloomington</t>
+          <t>Transfer 1 from Bloomington, 1 from Minnetonka, 1 from Roseville</t>
         </is>
       </c>
     </row>
@@ -23210,7 +23210,7 @@
       </c>
       <c r="M547" t="inlineStr">
         <is>
-          <t>Transfer 1 from Chanhassen</t>
+          <t>Transfer 1 from Andover</t>
         </is>
       </c>
     </row>
@@ -23306,7 +23306,7 @@
       </c>
       <c r="M549" t="inlineStr">
         <is>
-          <t>Transfer 1 from Andover</t>
+          <t>Transfer 1 from Chanhassen</t>
         </is>
       </c>
     </row>
@@ -24008,7 +24008,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="D566" t="n">
@@ -24054,7 +24054,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D567" t="n">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t>Transfer 2 from Minnetonka</t>
+          <t>Transfer 2 from Blaine</t>
         </is>
       </c>
     </row>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="M573" t="inlineStr">
         <is>
-          <t>Transfer 1 from Minnetonka, 1 from Bloomington</t>
+          <t>Transfer 1 from Chanhassen, 1 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="M574" t="inlineStr">
         <is>
-          <t>Transfer 2 from Bloomington</t>
+          <t>Transfer 2 from Chanhassen</t>
         </is>
       </c>
     </row>
@@ -24420,7 +24420,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -24451,7 +24451,7 @@
       </c>
       <c r="M576" t="inlineStr">
         <is>
-          <t>Transfer 3 from Chanhassen</t>
+          <t>Transfer 3 from Bloomington</t>
         </is>
       </c>
     </row>
@@ -24463,7 +24463,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -24950,7 +24950,7 @@
       </c>
       <c r="M588" t="inlineStr">
         <is>
-          <t>Transfer 1 from St. Louis Park</t>
+          <t>Transfer 1 from Cottage Grove</t>
         </is>
       </c>
     </row>
@@ -25199,25 +25199,20 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="D595" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E595" t="n">
         <v>0.5</v>
       </c>
       <c r="F595" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -25227,7 +25222,7 @@
       </c>
       <c r="M595" t="inlineStr">
         <is>
-          <t>Transfer 2 from Stillwater</t>
+          <t>Transfer 1 from Stillwater</t>
         </is>
       </c>
     </row>
@@ -25239,20 +25234,25 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Vadnais Heights</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D596" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E596" t="n">
         <v>0.5</v>
       </c>
       <c r="F596" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G596" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="M596" t="inlineStr">
         <is>
-          <t>Transfer 1 from Chanhassen</t>
+          <t>Transfer 2 from Stillwater</t>
         </is>
       </c>
     </row>
@@ -25639,7 +25639,7 @@
       </c>
       <c r="M605" t="inlineStr">
         <is>
-          <t>Transfer 1 from Stillwater</t>
+          <t>Transfer 1 from Ramsey</t>
         </is>
       </c>
     </row>
@@ -25981,7 +25981,7 @@
       </c>
       <c r="M613" t="inlineStr">
         <is>
-          <t>Transfer 2 from St. Louis Park, 1 from Ramsey</t>
+          <t>Transfer 2 from St. Louis Park, 1 from Chanhassen</t>
         </is>
       </c>
     </row>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -26117,7 +26117,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -26203,7 +26203,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -26527,7 +26527,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -26701,7 +26701,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -27332,25 +27332,20 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Plymouth</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="D646" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E646" t="n">
         <v>1.1</v>
       </c>
       <c r="F646" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G646" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H646" t="n">
         <v>0</v>
@@ -27360,7 +27355,7 @@
       </c>
       <c r="M646" t="inlineStr">
         <is>
-          <t>Transfer 4 from St. Louis Park</t>
+          <t>Transfer 3 from St. Louis Park</t>
         </is>
       </c>
     </row>
@@ -27372,20 +27367,25 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Plymouth</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D647" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E647" t="n">
         <v>1.1</v>
       </c>
       <c r="F647" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G647" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H647" t="n">
         <v>0</v>
@@ -27395,7 +27395,7 @@
       </c>
       <c r="M647" t="inlineStr">
         <is>
-          <t>Transfer 3 from St. Louis Park</t>
+          <t>Transfer 4 from St. Louis Park</t>
         </is>
       </c>
     </row>
@@ -27407,20 +27407,20 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="D648" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E648" t="n">
         <v>0.8</v>
       </c>
       <c r="F648" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G648" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -27436,7 +27436,7 @@
       </c>
       <c r="M648" t="inlineStr">
         <is>
-          <t>Transfer 1 from Ramsey</t>
+          <t>Transfer 2 from Andover</t>
         </is>
       </c>
     </row>
@@ -27489,20 +27489,20 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="D650" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E650" t="n">
         <v>0.8</v>
       </c>
       <c r="F650" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H650" t="n">
         <v>0</v>
@@ -27518,7 +27518,7 @@
       </c>
       <c r="M650" t="inlineStr">
         <is>
-          <t>Transfer 2 from Andover</t>
+          <t>Transfer 1 from Andover</t>
         </is>
       </c>
     </row>
@@ -27653,7 +27653,7 @@
       </c>
       <c r="M653" t="inlineStr">
         <is>
-          <t>Transfer 1 from Osseo</t>
+          <t>Transfer 1 from Bloomington</t>
         </is>
       </c>
     </row>
@@ -28015,7 +28015,7 @@
       </c>
       <c r="M662" t="inlineStr">
         <is>
-          <t>Transfer 2 from Minneapolis</t>
+          <t>Transfer 2 from Andover</t>
         </is>
       </c>
     </row>
@@ -28176,7 +28176,7 @@
       </c>
       <c r="M666" t="inlineStr">
         <is>
-          <t>Transfer 3 from Osseo</t>
+          <t>Transfer 3 from Cottage Grove</t>
         </is>
       </c>
     </row>
@@ -28269,25 +28269,20 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Plymouth</t>
-        </is>
-      </c>
-      <c r="C669" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="D669" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E669" t="n">
         <v>0.9</v>
       </c>
       <c r="F669" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G669" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H669" t="n">
         <v>0</v>
@@ -28300,7 +28295,7 @@
       </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>Transfer 3 from Bloomington</t>
+          <t>Transfer 2 from Bloomington</t>
         </is>
       </c>
     </row>
@@ -28312,20 +28307,25 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>St. Louis Park</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D670" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E670" t="n">
         <v>0.9</v>
       </c>
       <c r="F670" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G670" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -28338,7 +28338,7 @@
       </c>
       <c r="M670" t="inlineStr">
         <is>
-          <t>Transfer 1 from Andover, 1 from Bloomington</t>
+          <t>Transfer 2 from Minnetonka, 1 from Bloomington</t>
         </is>
       </c>
     </row>
@@ -28350,7 +28350,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -28393,7 +28393,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -28424,7 +28424,7 @@
       </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>Transfer 2 from Minnetonka, 1 from Andover</t>
+          <t>Transfer 2 from Andover, 1 from Bloomington</t>
         </is>
       </c>
     </row>
@@ -28467,7 +28467,7 @@
       </c>
       <c r="M673" t="inlineStr">
         <is>
-          <t>Transfer 1 from Cottage Grove, 1 from Bloomington; BUY 1</t>
+          <t>Transfer 1 from Cottage Grove, 1 from Ramsey; BUY 1</t>
         </is>
       </c>
     </row>
@@ -29377,25 +29377,20 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Rosemount</t>
-        </is>
-      </c>
-      <c r="C696" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="D696" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E696" t="n">
         <v>0.5</v>
       </c>
       <c r="F696" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -29405,7 +29400,7 @@
       </c>
       <c r="M696" t="inlineStr">
         <is>
-          <t>Transfer 2 from Osseo</t>
+          <t>Transfer 1 from Osseo</t>
         </is>
       </c>
     </row>
@@ -29417,20 +29412,25 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Rosemount</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D697" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E697" t="n">
         <v>0.5</v>
       </c>
       <c r="F697" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G697" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H697" t="n">
         <v>0</v>
@@ -29440,7 +29440,7 @@
       </c>
       <c r="M697" t="inlineStr">
         <is>
-          <t>Transfer 1 from Plymouth</t>
+          <t>Transfer 2 from Plymouth</t>
         </is>
       </c>
     </row>
@@ -29836,7 +29836,7 @@
       </c>
       <c r="M706" t="inlineStr">
         <is>
-          <t>Transfer 1 from Vadnais Heights</t>
+          <t>Transfer 1 from St. Louis Park</t>
         </is>
       </c>
     </row>
@@ -29886,23 +29886,28 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D708" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E708" t="n">
         <v>0.8</v>
       </c>
       <c r="F708" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G708" t="n">
         <v>0</v>
       </c>
       <c r="H708" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I708" t="n">
         <v>10.88</v>
@@ -29912,7 +29917,7 @@
       </c>
       <c r="M708" t="inlineStr">
         <is>
-          <t>BUY 2</t>
+          <t>BUY 3</t>
         </is>
       </c>
     </row>
@@ -29924,28 +29929,23 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
-        </is>
-      </c>
-      <c r="C709" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="D709" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E709" t="n">
         <v>0.8</v>
       </c>
       <c r="F709" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G709" t="n">
         <v>0</v>
       </c>
       <c r="H709" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I709" t="n">
         <v>10.88</v>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="M709" t="inlineStr">
         <is>
-          <t>BUY 3</t>
+          <t>BUY 2</t>
         </is>
       </c>
     </row>
@@ -29967,25 +29967,20 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Roseville</t>
-        </is>
-      </c>
-      <c r="C710" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="D710" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E710" t="n">
         <v>0.8</v>
       </c>
       <c r="F710" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G710" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -29998,7 +29993,7 @@
       </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>Transfer 3 from Cottage Grove</t>
+          <t>Transfer 1 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -30086,20 +30081,25 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Roseville</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D713" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E713" t="n">
         <v>0.8</v>
       </c>
       <c r="F713" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G713" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -30112,7 +30112,7 @@
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>Transfer 1 from Minnetonka</t>
+          <t>Transfer 3 from Cottage Grove</t>
         </is>
       </c>
     </row>
@@ -30124,7 +30124,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -30338,7 +30338,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -30369,7 +30369,7 @@
       </c>
       <c r="M719" t="inlineStr">
         <is>
-          <t>Transfer 3 from Cottage Grove</t>
+          <t>Transfer 3 from Osseo</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="M722" t="inlineStr">
         <is>
-          <t>Transfer 2 from Stillwater</t>
+          <t>Transfer 2 from Bloomington</t>
         </is>
       </c>
     </row>
@@ -30553,20 +30553,20 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="D724" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E724" t="n">
         <v>0.8</v>
       </c>
       <c r="F724" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G724" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H724" t="n">
         <v>0</v>
@@ -30576,7 +30576,7 @@
       </c>
       <c r="M724" t="inlineStr">
         <is>
-          <t>Transfer 2 from St. Louis Park</t>
+          <t>Transfer 1 from St. Louis Park</t>
         </is>
       </c>
     </row>
@@ -30588,20 +30588,20 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="D725" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E725" t="n">
         <v>0.8</v>
       </c>
       <c r="F725" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G725" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M725" t="inlineStr">
         <is>
-          <t>Transfer 1 from Osseo</t>
+          <t>Transfer 2 from St. Louis Park</t>
         </is>
       </c>
     </row>
@@ -30892,7 +30892,7 @@
       </c>
       <c r="M732" t="inlineStr">
         <is>
-          <t>Transfer 2 from Andover</t>
+          <t>Transfer 2 from Minneapolis</t>
         </is>
       </c>
     </row>
@@ -31574,20 +31574,25 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Woodbury</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D749" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E749" t="n">
         <v>0.8</v>
       </c>
       <c r="F749" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G749" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -31600,7 +31605,7 @@
       </c>
       <c r="M749" t="inlineStr">
         <is>
-          <t>Transfer 1 from Rosemount</t>
+          <t>Transfer 3 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -31612,25 +31617,20 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Woodbury</t>
-        </is>
-      </c>
-      <c r="C750" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="D750" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E750" t="n">
         <v>0.8</v>
       </c>
       <c r="F750" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G750" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H750" t="n">
         <v>0</v>
@@ -31643,7 +31643,7 @@
       </c>
       <c r="M750" t="inlineStr">
         <is>
-          <t>Transfer 3 from Minnetonka</t>
+          <t>Transfer 1 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -32551,7 +32551,7 @@
       </c>
       <c r="M772" t="inlineStr">
         <is>
-          <t>Transfer 2 from Rosemount</t>
+          <t>Transfer 2 from Plymouth</t>
         </is>
       </c>
     </row>
@@ -32597,7 +32597,7 @@
       </c>
       <c r="M773" t="inlineStr">
         <is>
-          <t>Transfer 2 from Chanhassen</t>
+          <t>Transfer 2 from Cottage Grove</t>
         </is>
       </c>
     </row>
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M780" t="inlineStr">
         <is>
-          <t>Transfer 2 from St. Louis Park</t>
+          <t>Transfer 2 from Woodbury</t>
         </is>
       </c>
     </row>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -33478,7 +33478,7 @@
       </c>
       <c r="M794" t="inlineStr">
         <is>
-          <t>Transfer 1 from Rosemount</t>
+          <t>Transfer 1 from Osseo</t>
         </is>
       </c>
     </row>
@@ -33518,7 +33518,7 @@
       </c>
       <c r="M795" t="inlineStr">
         <is>
-          <t>Transfer 1 from Stillwater, 1 from Minneapolis</t>
+          <t>Transfer 1 from Minneapolis, 1 from St. Louis Park</t>
         </is>
       </c>
     </row>
@@ -34021,7 +34021,7 @@
       </c>
       <c r="M808" t="inlineStr">
         <is>
-          <t>Transfer 1 from Plymouth</t>
+          <t>Transfer 1 from Blaine</t>
         </is>
       </c>
     </row>
@@ -34076,7 +34076,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -34107,7 +34107,7 @@
       </c>
       <c r="M810" t="inlineStr">
         <is>
-          <t>Transfer 1 from Andover, 1 from Ramsey</t>
+          <t>Transfer 1 from Ramsey, 1 from Woodbury</t>
         </is>
       </c>
     </row>
@@ -34199,20 +34199,25 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Roseville</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D813" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E813" t="n">
         <v>0.5</v>
       </c>
       <c r="F813" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G813" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H813" t="n">
         <v>0</v>
@@ -34225,7 +34230,7 @@
       </c>
       <c r="M813" t="inlineStr">
         <is>
-          <t>Transfer 1 from Andover</t>
+          <t>Transfer 2 from Andover</t>
         </is>
       </c>
     </row>
@@ -34237,7 +34242,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -34316,7 +34321,7 @@
       </c>
       <c r="M815" t="inlineStr">
         <is>
-          <t>Transfer 1 from Vadnais Heights</t>
+          <t>Transfer 1 from Ramsey</t>
         </is>
       </c>
     </row>
@@ -34379,7 +34384,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -34430,25 +34435,20 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
-        </is>
-      </c>
-      <c r="C818" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="D818" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E818" t="n">
         <v>0.5</v>
       </c>
       <c r="F818" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G818" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H818" t="n">
         <v>1</v>
@@ -34461,7 +34461,7 @@
       </c>
       <c r="M818" t="inlineStr">
         <is>
-          <t>Transfer 1 from Woodbury; BUY 1</t>
+          <t>BUY 1</t>
         </is>
       </c>
     </row>
@@ -34513,7 +34513,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -34553,7 +34553,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -34797,25 +34797,20 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Ramsey</t>
-        </is>
-      </c>
-      <c r="C827" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D827" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E827" t="n">
         <v>0.4</v>
       </c>
       <c r="F827" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G827" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -34833,7 +34828,7 @@
       </c>
       <c r="M827" t="inlineStr">
         <is>
-          <t>Transfer 2 from Rosemount</t>
+          <t>Transfer 1 from Rosemount</t>
         </is>
       </c>
     </row>
@@ -34868,7 +34863,7 @@
       </c>
       <c r="M828" t="inlineStr">
         <is>
-          <t>Transfer 1 from Cottage Grove</t>
+          <t>Transfer 1 from St. Louis Park</t>
         </is>
       </c>
     </row>
@@ -34880,20 +34875,25 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Ramsey</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D829" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E829" t="n">
         <v>0.4</v>
       </c>
       <c r="F829" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G829" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -34911,7 +34911,7 @@
       </c>
       <c r="M829" t="inlineStr">
         <is>
-          <t>Transfer 1 from Plymouth</t>
+          <t>Transfer 2 from Rosemount</t>
         </is>
       </c>
     </row>
@@ -35021,7 +35021,7 @@
       </c>
       <c r="M832" t="inlineStr">
         <is>
-          <t>Transfer 2 from Minneapolis</t>
+          <t>Transfer 2 from Andover</t>
         </is>
       </c>
     </row>
@@ -37007,7 +37007,7 @@
       </c>
       <c r="M880" t="inlineStr">
         <is>
-          <t>Transfer 1 from Vadnais Heights</t>
+          <t>Transfer 1 from Minneapolis</t>
         </is>
       </c>
     </row>
@@ -37050,7 +37050,7 @@
       </c>
       <c r="M881" t="inlineStr">
         <is>
-          <t>Transfer 1 from Ramsey, 1 from Rosemount</t>
+          <t>Transfer 2 from Rosemount</t>
         </is>
       </c>
     </row>
@@ -37136,7 +37136,7 @@
       </c>
       <c r="M883" t="inlineStr">
         <is>
-          <t>Transfer 2 from Vadnais Heights</t>
+          <t>Transfer 2 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -37148,28 +37148,23 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>Stillwater</t>
-        </is>
-      </c>
-      <c r="C884" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E884" t="n">
         <v>0.5</v>
       </c>
       <c r="F884" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G884" t="n">
         <v>0</v>
       </c>
       <c r="H884" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I884" t="n">
         <v>7.93</v>
@@ -37179,7 +37174,7 @@
       </c>
       <c r="M884" t="inlineStr">
         <is>
-          <t>BUY 2</t>
+          <t>BUY 1</t>
         </is>
       </c>
     </row>
@@ -37191,7 +37186,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -37234,23 +37229,28 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Osseo</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D886" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E886" t="n">
         <v>0.5</v>
       </c>
       <c r="F886" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G886" t="n">
         <v>0</v>
       </c>
       <c r="H886" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I886" t="n">
         <v>7.93</v>
@@ -37260,7 +37260,7 @@
       </c>
       <c r="M886" t="inlineStr">
         <is>
-          <t>BUY 1</t>
+          <t>BUY 2</t>
         </is>
       </c>
     </row>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -37792,7 +37792,7 @@
       </c>
       <c r="M899" t="inlineStr">
         <is>
-          <t>Transfer 2 from Blaine</t>
+          <t>Transfer 2 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -37987,7 +37987,7 @@
       </c>
       <c r="M904" t="inlineStr">
         <is>
-          <t>Transfer 2 from Minnetonka</t>
+          <t>Transfer 2 from Blaine</t>
         </is>
       </c>
     </row>
@@ -38091,7 +38091,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -38131,7 +38131,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="M913" t="inlineStr">
         <is>
-          <t>Transfer 2 from Chanhassen</t>
+          <t>Transfer 2 from Bloomington</t>
         </is>
       </c>
     </row>
@@ -38428,7 +38428,7 @@
       </c>
       <c r="M914" t="inlineStr">
         <is>
-          <t>Transfer 1 from Stillwater</t>
+          <t>Transfer 1 from Plymouth</t>
         </is>
       </c>
     </row>
@@ -38514,7 +38514,7 @@
       </c>
       <c r="M916" t="inlineStr">
         <is>
-          <t>Transfer 2 from Ramsey</t>
+          <t>Transfer 2 from Chanhassen</t>
         </is>
       </c>
     </row>
@@ -38652,7 +38652,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
@@ -38680,7 +38680,7 @@
       </c>
       <c r="M920" t="inlineStr">
         <is>
-          <t>Transfer 2 from Roseville</t>
+          <t>Transfer 2 from Vadnais Heights</t>
         </is>
       </c>
     </row>
@@ -38743,7 +38743,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -38771,7 +38771,7 @@
       </c>
       <c r="M922" t="inlineStr">
         <is>
-          <t>Transfer 2 from Vadnais Heights</t>
+          <t>Transfer 2 from Roseville</t>
         </is>
       </c>
     </row>
@@ -39234,7 +39234,7 @@
       </c>
       <c r="M933" t="inlineStr">
         <is>
-          <t>Transfer 1 from Ramsey</t>
+          <t>Transfer 1 from Stillwater</t>
         </is>
       </c>
     </row>
@@ -39378,7 +39378,7 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="M939" t="inlineStr">
         <is>
-          <t>Transfer 1 from Minneapolis, 1 from Minnetonka</t>
+          <t>Transfer 1 from Minneapolis, 1 from Ramsey</t>
         </is>
       </c>
     </row>
@@ -40614,7 +40614,7 @@
       </c>
       <c r="M966" t="inlineStr">
         <is>
-          <t>Transfer 1 from Minnetonka</t>
+          <t>Transfer 1 from Vadnais Heights</t>
         </is>
       </c>
     </row>
@@ -40904,7 +40904,7 @@
       </c>
       <c r="M973" t="inlineStr">
         <is>
-          <t>Transfer 2 from Rosemount</t>
+          <t>Transfer 2 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -41310,7 +41310,7 @@
       </c>
       <c r="M983" t="inlineStr">
         <is>
-          <t>Transfer 2 from Ramsey</t>
+          <t>Transfer 2 from Chanhassen</t>
         </is>
       </c>
     </row>
@@ -41322,7 +41322,7 @@
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
@@ -41368,7 +41368,7 @@
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -41740,7 +41740,7 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
@@ -41780,7 +41780,7 @@
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -41820,7 +41820,7 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="M1002" t="inlineStr">
         <is>
-          <t>Transfer 1 from Andover</t>
+          <t>Transfer 1 from Ramsey</t>
         </is>
       </c>
     </row>
@@ -42118,7 +42118,7 @@
       </c>
       <c r="M1003" t="inlineStr">
         <is>
-          <t>Transfer 1 from Stillwater</t>
+          <t>Transfer 1 from Ramsey</t>
         </is>
       </c>
     </row>
@@ -42130,20 +42130,25 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Vadnais Heights</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D1004" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1004" t="n">
         <v>0.4</v>
       </c>
       <c r="F1004" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1004" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -42164,7 +42169,7 @@
       </c>
       <c r="M1004" t="inlineStr">
         <is>
-          <t>Transfer 1 from Osseo</t>
+          <t>Transfer 2 from Osseo</t>
         </is>
       </c>
     </row>
@@ -42210,7 +42215,7 @@
       </c>
       <c r="M1005" t="inlineStr">
         <is>
-          <t>Transfer 2 from Minnetonka</t>
+          <t>Transfer 2 from Minneapolis</t>
         </is>
       </c>
     </row>
@@ -42337,7 +42342,7 @@
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -42451,7 +42456,7 @@
       </c>
       <c r="M1011" t="inlineStr">
         <is>
-          <t>Transfer 1 from Minneapolis</t>
+          <t>Transfer 1 from Cottage Grove</t>
         </is>
       </c>
     </row>
@@ -42514,7 +42519,7 @@
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
@@ -42724,7 +42729,7 @@
       </c>
       <c r="M1017" t="inlineStr">
         <is>
-          <t>Transfer 1 from St. Louis Park</t>
+          <t>Transfer 1 from Stillwater</t>
         </is>
       </c>
     </row>
@@ -42945,25 +42950,20 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
-        </is>
-      </c>
-      <c r="C1023" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="D1023" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1023" t="n">
         <v>0.4</v>
       </c>
       <c r="F1023" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1023" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -42984,7 +42984,7 @@
       </c>
       <c r="M1023" t="inlineStr">
         <is>
-          <t>Transfer 2 from Chanhassen</t>
+          <t>Transfer 1 from Chanhassen</t>
         </is>
       </c>
     </row>
@@ -43076,7 +43076,7 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
@@ -43116,7 +43116,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
@@ -43156,7 +43156,7 @@
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
@@ -43196,7 +43196,7 @@
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
@@ -43719,7 +43719,7 @@
       </c>
       <c r="M1041" t="inlineStr">
         <is>
-          <t>Transfer 1 from Ramsey</t>
+          <t>Transfer 1 from Vadnais Heights</t>
         </is>
       </c>
     </row>
@@ -43934,20 +43934,25 @@
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D1047" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1047" t="n">
         <v>0.5</v>
       </c>
       <c r="F1047" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1047" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -43968,7 +43973,7 @@
       </c>
       <c r="M1047" t="inlineStr">
         <is>
-          <t>Transfer 1 from Ramsey</t>
+          <t>Transfer 2 from Rosemount</t>
         </is>
       </c>
     </row>
@@ -44112,25 +44117,20 @@
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
-        </is>
-      </c>
-      <c r="C1051" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="D1051" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1051" t="n">
         <v>0.5</v>
       </c>
       <c r="F1051" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1051" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -44151,7 +44151,7 @@
       </c>
       <c r="M1051" t="inlineStr">
         <is>
-          <t>Transfer 2 from Plymouth</t>
+          <t>Transfer 1 from Ramsey</t>
         </is>
       </c>
     </row>
@@ -44191,7 +44191,7 @@
       </c>
       <c r="M1052" t="inlineStr">
         <is>
-          <t>Transfer 1 from Minnetonka</t>
+          <t>Transfer 1 from Andover</t>
         </is>
       </c>
     </row>
@@ -44203,7 +44203,7 @@
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
@@ -44243,7 +44243,7 @@
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
@@ -44523,7 +44523,7 @@
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
@@ -44735,7 +44735,7 @@
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
@@ -44778,7 +44778,7 @@
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
@@ -44892,7 +44892,7 @@
       </c>
       <c r="M1069" t="inlineStr">
         <is>
-          <t>Transfer 1 from Stillwater</t>
+          <t>Transfer 1 from Blaine</t>
         </is>
       </c>
     </row>
@@ -44904,28 +44904,23 @@
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>Ramsey</t>
-        </is>
-      </c>
-      <c r="C1070" t="inlineStr">
-        <is>
-          <t>STOCKOUT</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="D1070" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1070" t="n">
         <v>0.4</v>
       </c>
       <c r="F1070" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1070" t="n">
         <v>0</v>
       </c>
       <c r="H1070" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1070" t="n">
         <v>5.44</v>
@@ -44935,7 +44930,7 @@
       </c>
       <c r="M1070" t="inlineStr">
         <is>
-          <t>BUY 2</t>
+          <t>BUY 1</t>
         </is>
       </c>
     </row>
@@ -44947,23 +44942,28 @@
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Ramsey</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="D1071" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1071" t="n">
         <v>0.4</v>
       </c>
       <c r="F1071" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1071" t="n">
         <v>0</v>
       </c>
       <c r="H1071" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1071" t="n">
         <v>5.44</v>
@@ -44973,7 +44973,7 @@
       </c>
       <c r="M1071" t="inlineStr">
         <is>
-          <t>BUY 1</t>
+          <t>BUY 2</t>
         </is>
       </c>
     </row>
@@ -45127,7 +45127,7 @@
       </c>
       <c r="M1075" t="inlineStr">
         <is>
-          <t>Transfer 1 from Bloomington</t>
+          <t>Transfer 1 from Ramsey</t>
         </is>
       </c>
     </row>
@@ -46696,7 +46696,7 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C1114" t="inlineStr">
@@ -46776,7 +46776,7 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C1116" t="inlineStr">
@@ -46816,7 +46816,7 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
@@ -46856,7 +46856,7 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C1118" t="inlineStr">
@@ -46976,7 +46976,7 @@
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C1121" t="inlineStr">
@@ -47056,7 +47056,7 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
@@ -47807,7 +47807,7 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
@@ -48014,7 +48014,7 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
@@ -48507,7 +48507,7 @@
       </c>
       <c r="M1157" t="inlineStr">
         <is>
-          <t>Transfer 1 from Vadnais Heights</t>
+          <t>Transfer 1 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -48519,7 +48519,7 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
@@ -48605,7 +48605,7 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
@@ -48682,7 +48682,7 @@
       </c>
       <c r="M1161" t="inlineStr">
         <is>
-          <t>Transfer 1 from Stillwater</t>
+          <t>Transfer 1 from Andover</t>
         </is>
       </c>
     </row>
@@ -49091,7 +49091,7 @@
       </c>
       <c r="M1171" t="inlineStr">
         <is>
-          <t>Transfer 1 from Andover</t>
+          <t>Transfer 1 from Blaine</t>
         </is>
       </c>
     </row>
@@ -49741,7 +49741,7 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
@@ -49781,7 +49781,7 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
@@ -49986,7 +49986,7 @@
       </c>
       <c r="M1192" t="inlineStr">
         <is>
-          <t>Transfer 1 from Vadnais Heights</t>
+          <t>Transfer 1 from Blaine</t>
         </is>
       </c>
     </row>
@@ -51240,7 +51240,7 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C1223" t="inlineStr">
@@ -51280,7 +51280,7 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C1224" t="inlineStr">
@@ -51446,7 +51446,7 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C1228" t="inlineStr">
@@ -51646,7 +51646,7 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C1233" t="inlineStr">
@@ -51766,7 +51766,7 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C1236" t="inlineStr">
@@ -51846,7 +51846,7 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C1238" t="inlineStr">
@@ -51886,7 +51886,7 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C1239" t="inlineStr">
@@ -51926,7 +51926,7 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C1240" t="inlineStr">
@@ -52255,7 +52255,7 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C1248" t="inlineStr">
@@ -52406,7 +52406,7 @@
       </c>
       <c r="M1251" t="inlineStr">
         <is>
-          <t>Transfer 1 from Ramsey</t>
+          <t>Transfer 1 from Stillwater</t>
         </is>
       </c>
     </row>
@@ -52706,7 +52706,7 @@
       </c>
       <c r="M1258" t="inlineStr">
         <is>
-          <t>Transfer 1 from Bloomington</t>
+          <t>Transfer 1 from Blaine</t>
         </is>
       </c>
     </row>
@@ -53083,7 +53083,7 @@
       </c>
       <c r="M1267" t="inlineStr">
         <is>
-          <t>Transfer 1 from Rosemount</t>
+          <t>Transfer 1 from Osseo</t>
         </is>
       </c>
     </row>
@@ -53095,7 +53095,7 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C1268" t="inlineStr">
@@ -53135,7 +53135,7 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C1269" t="inlineStr">
@@ -53295,7 +53295,7 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C1273" t="inlineStr">
@@ -53335,7 +53335,7 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C1274" t="inlineStr">
@@ -53547,7 +53547,7 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C1279" t="inlineStr">
@@ -53627,7 +53627,7 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C1281" t="inlineStr">
@@ -53667,7 +53667,7 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C1282" t="inlineStr">
@@ -54027,7 +54027,7 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C1291" t="inlineStr">
@@ -54067,7 +54067,7 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C1292" t="inlineStr">
@@ -54107,7 +54107,7 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C1293" t="inlineStr">
@@ -54482,7 +54482,7 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C1302" t="inlineStr">
@@ -54522,7 +54522,7 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C1303" t="inlineStr">
@@ -54648,7 +54648,7 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C1306" t="inlineStr">
@@ -54688,7 +54688,7 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr">
@@ -54768,7 +54768,7 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr">
@@ -55516,7 +55516,7 @@
       </c>
       <c r="M1326" t="inlineStr">
         <is>
-          <t>Transfer 1 from Vadnais Heights</t>
+          <t>Transfer 1 from Rosemount</t>
         </is>
       </c>
     </row>
@@ -55652,7 +55652,7 @@
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C1330" t="inlineStr">
@@ -55824,7 +55824,7 @@
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C1334" t="inlineStr">
@@ -55864,7 +55864,7 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C1335" t="inlineStr">
@@ -56104,7 +56104,7 @@
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C1341" t="inlineStr">
@@ -56310,7 +56310,7 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C1346" t="inlineStr">
@@ -56350,7 +56350,7 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C1347" t="inlineStr">
@@ -56390,7 +56390,7 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C1348" t="inlineStr">
@@ -56430,7 +56430,7 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C1349" t="inlineStr">
@@ -57223,7 +57223,7 @@
       </c>
       <c r="M1368" t="inlineStr">
         <is>
-          <t>Transfer 1 from Blaine</t>
+          <t>Transfer 1 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -57521,7 +57521,7 @@
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C1376" t="inlineStr">
@@ -57567,7 +57567,7 @@
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C1377" t="inlineStr">
@@ -57693,7 +57693,7 @@
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C1380" t="inlineStr">
@@ -57733,7 +57733,7 @@
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C1381" t="inlineStr">
@@ -57773,7 +57773,7 @@
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C1382" t="inlineStr">
@@ -57899,7 +57899,7 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Bloomington</t>
         </is>
       </c>
       <c r="C1385" t="inlineStr">
@@ -57939,7 +57939,7 @@
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>Bloomington</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C1386" t="inlineStr">
@@ -57979,7 +57979,7 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr">
@@ -58059,7 +58059,7 @@
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>Bloomington</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C1389" t="inlineStr">
@@ -58139,7 +58139,7 @@
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Bloomington</t>
         </is>
       </c>
       <c r="C1391" t="inlineStr">
@@ -58259,7 +58259,7 @@
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C1394" t="inlineStr">
@@ -58339,7 +58339,7 @@
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C1396" t="inlineStr">
@@ -58419,7 +58419,7 @@
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C1398" t="inlineStr">
@@ -58459,7 +58459,7 @@
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C1399" t="inlineStr">
@@ -58539,7 +58539,7 @@
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr">
@@ -58828,7 +58828,7 @@
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C1408" t="inlineStr">
@@ -58868,7 +58868,7 @@
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C1409" t="inlineStr">
@@ -59379,7 +59379,7 @@
       </c>
       <c r="M1421" t="inlineStr">
         <is>
-          <t>Transfer 1 from Osseo</t>
+          <t>Transfer 1 from Minnetonka</t>
         </is>
       </c>
     </row>
@@ -60191,7 +60191,7 @@
       </c>
       <c r="M1441" t="inlineStr">
         <is>
-          <t>Transfer 1 from Blaine</t>
+          <t>Transfer 1 from Bloomington</t>
         </is>
       </c>
     </row>
@@ -60403,7 +60403,7 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C1447" t="inlineStr">
@@ -60643,7 +60643,7 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr">
@@ -61545,7 +61545,7 @@
       </c>
       <c r="M1474" t="inlineStr">
         <is>
-          <t>Transfer 1 from Woodbury</t>
+          <t>Transfer 1 from Minneapolis</t>
         </is>
       </c>
     </row>
@@ -61717,7 +61717,7 @@
       </c>
       <c r="M1478" t="inlineStr">
         <is>
-          <t>Transfer 1 from Chanhassen</t>
+          <t>Transfer 1 from Osseo</t>
         </is>
       </c>
     </row>
@@ -62023,7 +62023,7 @@
       </c>
       <c r="M1485" t="inlineStr">
         <is>
-          <t>Transfer 1 from Osseo</t>
+          <t>Transfer 1 from Plymouth</t>
         </is>
       </c>
     </row>
@@ -62075,7 +62075,7 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C1487" t="inlineStr">
@@ -62521,7 +62521,7 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C1498" t="inlineStr">
@@ -62561,7 +62561,7 @@
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C1499" t="inlineStr">
@@ -62681,7 +62681,7 @@
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C1502" t="inlineStr">
@@ -62721,7 +62721,7 @@
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C1503" t="inlineStr">
@@ -62761,7 +62761,7 @@
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr">
@@ -62801,7 +62801,7 @@
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr">
@@ -62841,7 +62841,7 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C1506" t="inlineStr">
@@ -62881,7 +62881,7 @@
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C1507" t="inlineStr">
@@ -63001,7 +63001,7 @@
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr">
@@ -63041,7 +63041,7 @@
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>Bloomington</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr">
@@ -63327,7 +63327,7 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Bloomington</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr">
@@ -63656,7 +63656,7 @@
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>Bloomington</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C1526" t="inlineStr">
@@ -63696,7 +63696,7 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr">
@@ -63776,7 +63776,7 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Bloomington</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr">
@@ -63816,7 +63816,7 @@
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C1530" t="inlineStr">
@@ -63856,7 +63856,7 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>Bloomington</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr">
@@ -64096,7 +64096,7 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C1537" t="inlineStr">
@@ -64136,7 +64136,7 @@
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C1538" t="inlineStr">
@@ -64176,7 +64176,7 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr">
@@ -64216,7 +64216,7 @@
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C1540" t="inlineStr">
@@ -64296,7 +64296,7 @@
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Bloomington</t>
         </is>
       </c>
       <c r="C1542" t="inlineStr">
@@ -64416,7 +64416,7 @@
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Bloomington</t>
         </is>
       </c>
       <c r="C1545" t="inlineStr">
@@ -64462,7 +64462,7 @@
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>Bloomington</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C1546" t="inlineStr">
@@ -64794,7 +64794,7 @@
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C1554" t="inlineStr">
@@ -64834,7 +64834,7 @@
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C1555" t="inlineStr">
@@ -64954,7 +64954,7 @@
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>Bloomington</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C1558" t="inlineStr">
@@ -65034,7 +65034,7 @@
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Bloomington</t>
         </is>
       </c>
       <c r="C1560" t="inlineStr">

--- a/data/THC Daily Buying Brief.xlsx
+++ b/data/THC Daily Buying Brief.xlsx
@@ -10,10 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brief" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Restock &amp; Transfer" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Flags" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy Ahead" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Restock &amp; Transfer'!$A$1:$M$1563</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pricing Flags'!$A$1:$E$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Buy Ahead'!$A$1:$F$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -428,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -480,195 +482,267 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TOP 15 ACTIONS (by weekly $ at risk):</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  $   470/wk [low     ] Looner 10mg THC Sodas Variety Pack 12pk  @ Andover        -&gt; Transfer 3 from Chanhassen</t>
-        </is>
-      </c>
-    </row>
+          <t>* 55 seasonal items to BUY AHEAD now (they peak next month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   419/wk [low     ] Leafy Maui Pineapple Gummies 5mg THC 10  @ St. Louis Park -&gt; Transfer 30 from Bloomington</t>
+          <t>TOP 15 ACTIONS (by weekly $ at risk):</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   401/wk [low     ] Uncle Arnie's Zen Green Tea 10mg THC 4pk @ Woodbury       -&gt; Transfer 10 from Blaine</t>
+          <t xml:space="preserve">  $   470/wk [low     ] Looner 10mg THC Sodas Variety Pack 12pk  @ Andover        -&gt; Transfer 3 from Chanhassen</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   342/wk [low     ] Looner 10mg THC Sodas Variety Pack 12pk  @ Rosemount      -&gt; Transfer 1 from Bloomington</t>
+          <t xml:space="preserve">  $   419/wk [low     ] Leafy Maui Pineapple Gummies 5mg THC 10  @ St. Louis Park -&gt; Transfer 30 from Bloomington</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   321/wk [low     ] Minny Grown Highbernate 2.0 10 Pack      @ Plymouth       -&gt; Transfer 22 from Chanhassen, 10 from Cottage Grove</t>
+          <t xml:space="preserve">  $   401/wk [low     ] Uncle Arnie's Zen Green Tea 10mg THC 4pk @ Woodbury       -&gt; Transfer 10 from Blaine</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   296/wk [low     ] Leafy Sour Watermelon Gummies 5mg THC 10 @ Minneapolis    -&gt; Transfer 39 from Bloomington</t>
+          <t xml:space="preserve">  $   342/wk [low     ] Looner 10mg THC Sodas Variety Pack 12pk  @ Rosemount      -&gt; Transfer 1 from Bloomington</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   258/wk [low     ] Minny Grown Highbernate 2.0 10 Pack      @ St. Louis Park -&gt; Transfer 1 from Osseo</t>
+          <t xml:space="preserve">  $   321/wk [low     ] Minny Grown Highbernate 2.0 10 Pack      @ Plymouth       -&gt; Transfer 22 from Chanhassen, 10 from Cottage Grove</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   257/wk [low     ] Gigli Extra Gigli Variety 10mg THC 4pk 1 @ Minneapolis    -&gt; Transfer 24 from Bloomington</t>
+          <t xml:space="preserve">  $   296/wk [low     ] Leafy Sour Watermelon Gummies 5mg THC 10 @ Minneapolis    -&gt; Transfer 39 from Bloomington</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   253/wk [low     ] Leafy Sour Blue Raspberry Gummies 5mg TH @ Minneapolis    -&gt; Transfer 53 from Bloomington</t>
+          <t xml:space="preserve">  $   258/wk [low     ] Minny Grown Highbernate 2.0 10 Pack      @ St. Louis Park -&gt; Transfer 1 from Osseo</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   248/wk [low     ] Leafy Maui Pineapple Gummies 5mg THC 10  @ Minneapolis    -&gt; Transfer 44 from Bloomington</t>
+          <t xml:space="preserve">  $   257/wk [low     ] Gigli Extra Gigli Variety 10mg THC 4pk 1 @ Minneapolis    -&gt; Transfer 24 from Bloomington</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   247/wk [low     ] Looner Professor Pepper 10mg THC 4pk 12o @ Andover        -&gt; Transfer 1 from Plymouth</t>
+          <t xml:space="preserve">  $   253/wk [low     ] Leafy Sour Blue Raspberry Gummies 5mg TH @ Minneapolis    -&gt; Transfer 53 from Bloomington</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   239/wk [STOCKOUT] Minny Grown Highbernate Moon Melon 5mg T @ Plymouth       -&gt; Transfer 30 from Minneapolis</t>
+          <t xml:space="preserve">  $   248/wk [low     ] Leafy Maui Pineapple Gummies 5mg THC 10  @ Minneapolis    -&gt; Transfer 44 from Bloomington</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   226/wk [low     ] Minny Grown St. Croix Sunrise 10 Pack    @ Plymouth       -&gt; Transfer 13 from Blaine</t>
+          <t xml:space="preserve">  $   247/wk [low     ] Looner Professor Pepper 10mg THC 4pk 12o @ Andover        -&gt; Transfer 1 from Plymouth</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   223/wk [low     ] Leafy Sour Blue Raspberry Gummies 5mg TH @ Osseo          -&gt; Transfer 6 from Bloomington</t>
+          <t xml:space="preserve">  $   239/wk [STOCKOUT] Minny Grown Highbernate Moon Melon 5mg T @ Plymouth       -&gt; Transfer 30 from Minneapolis</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  $   220/wk [low     ] Leafy Maui Pineapple Gummies 5mg THC 10  @ Roseville      -&gt; Transfer 18 from Bloomington</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+          <t xml:space="preserve">  $   226/wk [low     ] Minny Grown St. Croix Sunrise 10 Pack    @ Plymouth       -&gt; Transfer 13 from Blaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  $   223/wk [low     ] Leafy Sour Blue Raspberry Gummies 5mg TH @ Osseo          -&gt; Transfer 6 from Bloomington</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PRICING - top above market (review):</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  +  31%  Minny Grown Cabin Colada 5mg THC 10 Pack       ours $23.99 vs mkt $18.32</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  $   220/wk [low     ] Leafy Maui Pineapple Gummies 5mg THC 10  @ Roseville      -&gt; Transfer 18 from Bloomington</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  +  30%  Hop Dreams Day Dream 10mg THC 4pk 12oz can     ours $18.99 vs mkt $14.60</t>
+          <t>BUY AHEAD (seasonal - order extra now, these peak next month):</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  +  29%  Sweet Justice Lemonade Ginger Ale 10mg THC 4pk ours $18.99 vs mkt $14.77</t>
+          <t xml:space="preserve">  Minny Grown Highbernate 10 Pack              peaks Jul x1.25  (9608/yr)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  +  22%  Gigli Dark Chocolate 5mg THC 10 Pack           ours $18.99 vs mkt $15.52</t>
+          <t xml:space="preserve">  Uncle Arnie's Cherry Limeade 10mg THC 4pk 12 peaks Jul x1.32  (4726/yr)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  +  20%  Stigma Sleep Tonic 10mg THC 4pk 16oz can       ours $16.99 vs mkt $14.16</t>
+          <t xml:space="preserve">  Uncle Arnie's Rasp Lemonade 10mg THC 4pk 12o peaks Jul x1.27  (4320/yr)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PRICING - room to raise (below market):</t>
+          <t xml:space="preserve">  Leafy White Peach Bellini 10mg THC 12oz can  peaks Jul x1.65  (4307/yr)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">    -16%  Nibbana Grapefruit Glow 4pk 12oz can           ours $12.49 vs mkt $14.80</t>
+          <t xml:space="preserve">  Uncle Arnie's Straw Lemonade 10mg THC 4pk 12 peaks Jul x1.39  (3814/yr)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    -16%  Hectares 3mg Delta 9 2.5oz btl                 ours $5.24 vs mkt $6.21</t>
+          <t xml:space="preserve">  Leafy Sparkling Wild Straw Lemon Basil 10mg  peaks Jul x1.59  (3396/yr)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">    -16%  Earl Giles Chronic Tonic 5mg 4pk 12oz can      ours $11.49 vs mkt $13.68</t>
+          <t xml:space="preserve">  Minny Grown Mango 10 Pack                    peaks Jul x1.21  (3327/yr)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Leafy Sparkling Wild Cherry 10mg THC 12oz ca peaks Jul x1.43  (3263/yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PRICING - top above market (review):</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  +  31%  Minny Grown Cabin Colada 5mg THC 10 Pack       ours $23.99 vs mkt $18.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  +  30%  Hop Dreams Day Dream 10mg THC 4pk 12oz can     ours $18.99 vs mkt $14.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  +  29%  Sweet Justice Lemonade Ginger Ale 10mg THC 4pk ours $18.99 vs mkt $14.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  +  22%  Gigli Dark Chocolate 5mg THC 10 Pack           ours $18.99 vs mkt $15.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  +  20%  Stigma Sleep Tonic 10mg THC 4pk 16oz can       ours $16.99 vs mkt $14.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PRICING - room to raise (below market):</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -16%  Nibbana Grapefruit Glow 4pk 12oz can           ours $12.49 vs mkt $14.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -16%  Hectares 3mg Delta 9 2.5oz btl                 ours $5.24 vs mkt $6.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -16%  Earl Giles Chronic Tonic 5mg 4pk 12oz can      ours $11.49 vs mkt $13.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t xml:space="preserve">    -17%  Gigli Chocolate Variety 5mg THC 10 Pack        ours $15.24 vs mkt $18.43</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t xml:space="preserve">    -22%  Earl Giles Electric Lemonade 5mg 4pk 12oz can  ours $11.49 vs mkt $14.71</t>
         </is>
@@ -67117,4 +67191,1599 @@
   <autoFilter ref="A1:E90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Annual Units</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Peak Month</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Peak Index</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Buy-Ahead Month</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Minny Grown Highbernate 10 Pack</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Edibles</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>9608</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Uncle Arnie's Cherry Limeade 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4726</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Uncle Arnie's Rasp Lemonade 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4320</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Leafy White Peach Bellini 10mg THC 12oz can</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4307</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Uncle Arnie's Straw Lemonade 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3814</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Leafy Sparkling Wild Straw Lemon Basil 10mg THC 12oz can</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3396</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Minny Grown Mango 10 Pack</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Edibles</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Leafy Sparkling Wild Cherry 10mg THC 12oz can</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3263</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Uncle Arnie's Ice Tea Lemonade 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Brez Single 2.5mg THC 7.5oz can</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2731</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Looner Cr�me THC Soda 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2586</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Wild State Birdie Tea + Lemon Variety 10mg THC 9pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2217</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cann Roadie Lemon Lavender 2mg THC 0.5oz</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2171</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Leafy Raspberry Tea 10mg THC 12oz can</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2054</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Happy Duck Tangerine 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1998</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Brez 5mg THC Shots 2oz</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1777</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Voltage Tropical Frenzy 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1496</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1420</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>You Betcha Daytime 5mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1402</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gentlemen Smugglers 10mg THC 3 Pack</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1398</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sweet Leaves Peach 5mg THC 10 Pack</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Edibles</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1390</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Blackstack King Size Blackberry Lemonade THC 4pk 16oz can</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1271</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sweet Leaves Passion Fruit 5mg THC 10 Pack</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Edibles</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1254</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1236</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Wynk Raspberry Lemonade 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1225</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Acre Ginger Lime 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1133</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Wynk Strawberry Lemonade 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Voltage Mango-Colada 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1061</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Collective Project Mango Pineapple Coconut 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>898</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Collective Project Raspberry Vanilla 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>888</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Wyld Raspberry Sativa 10mg THC 5 Pack</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Edibles</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>869</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Wynk Lemonade 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>852</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Happi Raspberry Honeysuckle 4pk 7.5oz can</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>785</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DOPE Grapefruit 5mg THC 4pk 16oz can</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>599</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Clrty CoffeePot Mocha 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>548</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Vibes Pineapple Sativa 5mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>523</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Wild State Birdie Tea + Lemon 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>508</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Clrty Pineapple Hibiscus 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>506</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Brez Amplify 5mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>491</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Happy Duck Bomba 2.5mg THC 20 Pack</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Edibles</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>490</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>449</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Squoze Apple Kush 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>446</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>445</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gigli Caramel Mocha 5mg THC 10 Pack</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Edibles</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>414</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DOPE Pineapple 5mg THC 4pk 16oz can</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>375</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Sweet Justice Cola 5mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>357</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1906 Off Duty 5mg THC 10pk Snap</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Edibles</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>356</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Hectare's Watermelon Cucumber Mint 5mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>325</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Pamos Spritz Long Island 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>321</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Wynk Mandarin Pomeo 5mg THC 6pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>303</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Nibbana Blue Razz 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>293</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gigli Peppermint Crunch 5mg THC 10 Pack</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Edibles</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>278</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Nibbana Watermelon Wave 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>245</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Pamos Spritz Ranch Water 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>232</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>210</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F56"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/THC Daily Buying Brief.xlsx
+++ b/data/THC Daily Buying Brief.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Restock &amp; Transfer'!$A$1:$M$1563</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pricing Flags'!$A$1:$E$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pricing Flags'!$A$1:$I$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Buy Ahead'!$A$1:$F$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -65281,14 +65281,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -65304,15 +65308,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Total Wine</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cub</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Buncha Mkt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Market Price</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Vs</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Gap %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
@@ -65327,13 +65351,21 @@
       <c r="B2" t="n">
         <v>23.99</v>
       </c>
-      <c r="C2" t="n">
-        <v>18.32388888888889</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="F2" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>30.9</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65348,13 +65380,21 @@
       <c r="B3" t="n">
         <v>18.99</v>
       </c>
-      <c r="C3" t="n">
-        <v>14.60166666666667</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>30.1</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65369,13 +65409,21 @@
       <c r="B4" t="n">
         <v>18.99</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>14.77</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>28.6</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65390,13 +65438,21 @@
       <c r="B5" t="n">
         <v>18.99</v>
       </c>
-      <c r="C5" t="n">
-        <v>15.51833333333333</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>22.4</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65411,13 +65467,21 @@
       <c r="B6" t="n">
         <v>16.99</v>
       </c>
-      <c r="C6" t="n">
-        <v>14.15833333333333</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>20</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65432,13 +65496,21 @@
       <c r="B7" t="n">
         <v>47.49</v>
       </c>
-      <c r="C7" t="n">
-        <v>39.575</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="F7" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>20</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65453,13 +65525,21 @@
       <c r="B8" t="n">
         <v>23.99</v>
       </c>
-      <c r="C8" t="n">
-        <v>20.15666666666667</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="F8" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>19</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65474,13 +65554,21 @@
       <c r="B9" t="n">
         <v>22.49</v>
       </c>
-      <c r="C9" t="n">
-        <v>19.99111111111111</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>12.5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65495,13 +65583,21 @@
       <c r="B10" t="n">
         <v>12.99</v>
       </c>
-      <c r="C10" t="n">
-        <v>11.54666666666667</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>12.5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65516,13 +65612,21 @@
       <c r="B11" t="n">
         <v>36.99</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>32.88</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>12.5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65537,13 +65641,21 @@
       <c r="B12" t="n">
         <v>18.99</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>16.88</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>12.5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65558,13 +65670,21 @@
       <c r="B13" t="n">
         <v>14.99</v>
       </c>
-      <c r="C13" t="n">
-        <v>13.32444444444445</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="F13" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>12.5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65579,13 +65699,21 @@
       <c r="B14" t="n">
         <v>14.99</v>
       </c>
-      <c r="C14" t="n">
-        <v>13.32444444444445</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="F14" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>12.5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65600,13 +65728,21 @@
       <c r="B15" t="n">
         <v>14.99</v>
       </c>
-      <c r="C15" t="n">
-        <v>13.32444444444445</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>12.5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65621,13 +65757,21 @@
       <c r="B16" t="n">
         <v>18.99</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>16.88</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
         <v>12.5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65642,13 +65786,21 @@
       <c r="B17" t="n">
         <v>6.99</v>
       </c>
-      <c r="C17" t="n">
-        <v>6.213333333333334</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>12.5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65663,13 +65815,21 @@
       <c r="B18" t="n">
         <v>6.99</v>
       </c>
-      <c r="C18" t="n">
-        <v>6.213333333333334</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
         <v>12.5</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65684,13 +65844,21 @@
       <c r="B19" t="n">
         <v>12.49</v>
       </c>
-      <c r="C19" t="n">
-        <v>11.10222222222222</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
         <v>12.5</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65705,13 +65873,21 @@
       <c r="B20" t="n">
         <v>12.49</v>
       </c>
-      <c r="C20" t="n">
-        <v>11.10222222222222</v>
-      </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>12.5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65726,13 +65902,21 @@
       <c r="B21" t="n">
         <v>23.99</v>
       </c>
-      <c r="C21" t="n">
-        <v>21.32444444444444</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="F21" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
         <v>12.5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65747,13 +65931,21 @@
       <c r="B22" t="n">
         <v>12.99</v>
       </c>
-      <c r="C22" t="n">
-        <v>11.54666666666667</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
         <v>12.5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65768,13 +65960,21 @@
       <c r="B23" t="n">
         <v>22.49</v>
       </c>
-      <c r="C23" t="n">
-        <v>19.99111111111111</v>
-      </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F23" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
         <v>12.5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65789,13 +65989,21 @@
       <c r="B24" t="n">
         <v>22.49</v>
       </c>
-      <c r="C24" t="n">
-        <v>19.99111111111111</v>
-      </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F24" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
         <v>12.5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65810,13 +66018,21 @@
       <c r="B25" t="n">
         <v>12.99</v>
       </c>
-      <c r="C25" t="n">
-        <v>11.54666666666667</v>
-      </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="F25" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
         <v>12.5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65831,13 +66047,21 @@
       <c r="B26" t="n">
         <v>12.99</v>
       </c>
-      <c r="C26" t="n">
-        <v>11.54666666666667</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="F26" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
         <v>12.5</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65852,13 +66076,21 @@
       <c r="B27" t="n">
         <v>9.99</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
         <v>12.5</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65873,13 +66105,21 @@
       <c r="B28" t="n">
         <v>51.99</v>
       </c>
-      <c r="C28" t="n">
-        <v>46.21333333333334</v>
-      </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="F28" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
         <v>12.5</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65894,13 +66134,21 @@
       <c r="B29" t="n">
         <v>51.99</v>
       </c>
-      <c r="C29" t="n">
-        <v>46.21333333333334</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="F29" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
         <v>12.5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65915,13 +66163,21 @@
       <c r="B30" t="n">
         <v>17.99</v>
       </c>
-      <c r="C30" t="n">
-        <v>15.99111111111111</v>
-      </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="F30" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
         <v>12.5</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65936,13 +66192,21 @@
       <c r="B31" t="n">
         <v>23.99</v>
       </c>
-      <c r="C31" t="n">
-        <v>21.32444444444444</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="F31" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
         <v>12.5</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65957,13 +66221,21 @@
       <c r="B32" t="n">
         <v>23.99</v>
       </c>
-      <c r="C32" t="n">
-        <v>21.32444444444444</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
         <v>12.5</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65978,13 +66250,21 @@
       <c r="B33" t="n">
         <v>17.49</v>
       </c>
-      <c r="C33" t="n">
-        <v>15.54666666666667</v>
-      </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="F33" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
         <v>12.5</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -65999,13 +66279,21 @@
       <c r="B34" t="n">
         <v>9.99</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
         <v>12.5</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66020,13 +66308,21 @@
       <c r="B35" t="n">
         <v>48.49</v>
       </c>
-      <c r="C35" t="n">
-        <v>43.10222222222222</v>
-      </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
         <v>12.5</v>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66041,13 +66337,21 @@
       <c r="B36" t="n">
         <v>48.49</v>
       </c>
-      <c r="C36" t="n">
-        <v>43.10222222222222</v>
-      </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
         <v>12.5</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66062,13 +66366,21 @@
       <c r="B37" t="n">
         <v>14.99</v>
       </c>
-      <c r="C37" t="n">
-        <v>13.32444444444445</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="F37" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
         <v>12.5</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66083,13 +66395,21 @@
       <c r="B38" t="n">
         <v>11.49</v>
       </c>
-      <c r="C38" t="n">
-        <v>10.21333333333333</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
         <v>12.5</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66104,13 +66424,21 @@
       <c r="B39" t="n">
         <v>6.99</v>
       </c>
-      <c r="C39" t="n">
-        <v>6.213333333333334</v>
-      </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
         <v>12.5</v>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66125,13 +66453,21 @@
       <c r="B40" t="n">
         <v>6.99</v>
       </c>
-      <c r="C40" t="n">
-        <v>6.213333333333334</v>
-      </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
         <v>12.5</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66146,13 +66482,21 @@
       <c r="B41" t="n">
         <v>23.99</v>
       </c>
-      <c r="C41" t="n">
-        <v>21.32444444444444</v>
-      </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="F41" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
         <v>12.5</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66167,13 +66511,21 @@
       <c r="B42" t="n">
         <v>20.99</v>
       </c>
-      <c r="C42" t="n">
-        <v>18.65777777777778</v>
-      </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="F42" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
         <v>12.5</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66188,13 +66540,21 @@
       <c r="B43" t="n">
         <v>9.99</v>
       </c>
-      <c r="C43" t="n">
+      <c r="E43" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="D43" t="n">
+      <c r="F43" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
         <v>12.5</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66209,13 +66569,21 @@
       <c r="B44" t="n">
         <v>9.99</v>
       </c>
-      <c r="C44" t="n">
+      <c r="E44" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="D44" t="n">
+      <c r="F44" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
         <v>12.5</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66230,13 +66598,21 @@
       <c r="B45" t="n">
         <v>15.99</v>
       </c>
-      <c r="C45" t="n">
-        <v>14.21333333333333</v>
-      </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="F45" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
         <v>12.5</v>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66251,13 +66627,21 @@
       <c r="B46" t="n">
         <v>15.99</v>
       </c>
-      <c r="C46" t="n">
-        <v>14.21333333333333</v>
-      </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="F46" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
         <v>12.5</v>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66272,13 +66656,21 @@
       <c r="B47" t="n">
         <v>20.99</v>
       </c>
-      <c r="C47" t="n">
-        <v>18.65777777777778</v>
-      </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="F47" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
         <v>12.5</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66293,13 +66685,21 @@
       <c r="B48" t="n">
         <v>15.99</v>
       </c>
-      <c r="C48" t="n">
-        <v>14.21333333333333</v>
-      </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="F48" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
         <v>12.5</v>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66314,13 +66714,21 @@
       <c r="B49" t="n">
         <v>15.99</v>
       </c>
-      <c r="C49" t="n">
-        <v>14.21333333333333</v>
-      </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="F49" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
         <v>12.5</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66335,13 +66743,21 @@
       <c r="B50" t="n">
         <v>15.99</v>
       </c>
-      <c r="C50" t="n">
-        <v>14.21333333333333</v>
-      </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="F50" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
         <v>12.5</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66356,13 +66772,21 @@
       <c r="B51" t="n">
         <v>17.99</v>
       </c>
-      <c r="C51" t="n">
-        <v>15.99111111111111</v>
-      </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="F51" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
         <v>12.5</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66377,13 +66801,21 @@
       <c r="B52" t="n">
         <v>17.99</v>
       </c>
-      <c r="C52" t="n">
-        <v>15.99111111111111</v>
-      </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="F52" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
         <v>12.5</v>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66398,13 +66830,21 @@
       <c r="B53" t="n">
         <v>9.99</v>
       </c>
-      <c r="C53" t="n">
+      <c r="E53" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="D53" t="n">
+      <c r="F53" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
         <v>12.5</v>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66419,13 +66859,21 @@
       <c r="B54" t="n">
         <v>9.99</v>
       </c>
-      <c r="C54" t="n">
+      <c r="E54" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="D54" t="n">
+      <c r="F54" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
         <v>12.5</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66440,13 +66888,21 @@
       <c r="B55" t="n">
         <v>39.99</v>
       </c>
-      <c r="C55" t="n">
-        <v>35.54666666666667</v>
-      </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="F55" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
         <v>12.5</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66461,13 +66917,21 @@
       <c r="B56" t="n">
         <v>14.99</v>
       </c>
-      <c r="C56" t="n">
-        <v>13.32444444444445</v>
-      </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="F56" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
         <v>12.5</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66482,13 +66946,21 @@
       <c r="B57" t="n">
         <v>14.99</v>
       </c>
-      <c r="C57" t="n">
-        <v>13.32444444444445</v>
-      </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="F57" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
         <v>12.5</v>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66503,13 +66975,21 @@
       <c r="B58" t="n">
         <v>14.99</v>
       </c>
-      <c r="C58" t="n">
-        <v>13.32444444444445</v>
-      </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="F58" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
         <v>12.5</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66524,13 +67004,21 @@
       <c r="B59" t="n">
         <v>22.99</v>
       </c>
-      <c r="C59" t="n">
-        <v>20.43555555555555</v>
-      </c>
-      <c r="D59" t="n">
+      <c r="E59" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="F59" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
         <v>12.5</v>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66545,13 +67033,21 @@
       <c r="B60" t="n">
         <v>11.49</v>
       </c>
-      <c r="C60" t="n">
-        <v>10.21333333333333</v>
-      </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="F60" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
         <v>12.5</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66566,13 +67062,21 @@
       <c r="B61" t="n">
         <v>11.49</v>
       </c>
-      <c r="C61" t="n">
-        <v>10.21333333333333</v>
-      </c>
-      <c r="D61" t="n">
+      <c r="E61" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="F61" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
         <v>12.5</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66587,13 +67091,21 @@
       <c r="B62" t="n">
         <v>17.99</v>
       </c>
-      <c r="C62" t="n">
-        <v>15.99111111111111</v>
-      </c>
-      <c r="D62" t="n">
+      <c r="E62" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="F62" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
         <v>12.5</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66608,13 +67120,21 @@
       <c r="B63" t="n">
         <v>17.99</v>
       </c>
-      <c r="C63" t="n">
-        <v>15.99111111111111</v>
-      </c>
-      <c r="D63" t="n">
+      <c r="E63" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="F63" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
         <v>12.5</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66629,13 +67149,21 @@
       <c r="B64" t="n">
         <v>9.99</v>
       </c>
-      <c r="C64" t="n">
+      <c r="E64" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="D64" t="n">
+      <c r="F64" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
         <v>12.5</v>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66650,13 +67178,21 @@
       <c r="B65" t="n">
         <v>9.99</v>
       </c>
-      <c r="C65" t="n">
+      <c r="E65" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="D65" t="n">
+      <c r="F65" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
         <v>12.5</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66671,13 +67207,21 @@
       <c r="B66" t="n">
         <v>15.99</v>
       </c>
-      <c r="C66" t="n">
-        <v>14.21333333333333</v>
-      </c>
-      <c r="D66" t="n">
+      <c r="E66" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="F66" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
         <v>12.5</v>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66692,13 +67236,21 @@
       <c r="B67" t="n">
         <v>17.99</v>
       </c>
-      <c r="C67" t="n">
-        <v>15.99111111111111</v>
-      </c>
-      <c r="D67" t="n">
+      <c r="E67" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="F67" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
         <v>12.5</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66713,13 +67265,21 @@
       <c r="B68" t="n">
         <v>17.49</v>
       </c>
-      <c r="C68" t="n">
-        <v>15.62888888888889</v>
-      </c>
-      <c r="D68" t="n">
+      <c r="E68" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="F68" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
         <v>11.9</v>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66734,13 +67294,21 @@
       <c r="B69" t="n">
         <v>37.99</v>
       </c>
-      <c r="C69" t="n">
-        <v>34.21277777777778</v>
-      </c>
-      <c r="D69" t="n">
+      <c r="E69" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="F69" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
         <v>11</v>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>ABOVE market (review)</t>
         </is>
@@ -66755,13 +67323,21 @@
       <c r="B70" t="n">
         <v>12.49</v>
       </c>
-      <c r="C70" t="n">
-        <v>14.79555555555556</v>
-      </c>
-      <c r="D70" t="n">
+      <c r="E70" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F70" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
         <v>-15.6</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -66776,13 +67352,21 @@
       <c r="B71" t="n">
         <v>5.24</v>
       </c>
-      <c r="C71" t="n">
-        <v>6.212222222222223</v>
-      </c>
-      <c r="D71" t="n">
+      <c r="E71" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="F71" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
         <v>-15.7</v>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -66797,13 +67381,21 @@
       <c r="B72" t="n">
         <v>11.49</v>
       </c>
-      <c r="C72" t="n">
-        <v>13.68444444444444</v>
-      </c>
-      <c r="D72" t="n">
+      <c r="E72" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="F72" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
         <v>-16</v>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -66818,13 +67410,21 @@
       <c r="B73" t="n">
         <v>15.24</v>
       </c>
-      <c r="C73" t="n">
-        <v>18.435</v>
-      </c>
-      <c r="D73" t="n">
+      <c r="E73" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="F73" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
         <v>-17.3</v>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -66839,13 +67439,21 @@
       <c r="B74" t="n">
         <v>11.49</v>
       </c>
-      <c r="C74" t="n">
-        <v>14.71222222222222</v>
-      </c>
-      <c r="D74" t="n">
+      <c r="E74" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="F74" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
         <v>-21.9</v>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -66860,13 +67468,21 @@
       <c r="B75" t="n">
         <v>11.24</v>
       </c>
-      <c r="C75" t="n">
-        <v>14.68444444444444</v>
-      </c>
-      <c r="D75" t="n">
+      <c r="E75" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
         <v>-23.5</v>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -66881,13 +67497,21 @@
       <c r="B76" t="n">
         <v>19.24</v>
       </c>
-      <c r="C76" t="n">
-        <v>25.18444444444444</v>
-      </c>
-      <c r="D76" t="n">
+      <c r="E76" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="F76" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
         <v>-23.6</v>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -66902,13 +67526,21 @@
       <c r="B77" t="n">
         <v>14.99</v>
       </c>
-      <c r="C77" t="n">
-        <v>19.76777777777778</v>
-      </c>
-      <c r="D77" t="n">
+      <c r="E77" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="F77" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
         <v>-24.2</v>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -66923,13 +67555,21 @@
       <c r="B78" t="n">
         <v>14.99</v>
       </c>
-      <c r="C78" t="n">
-        <v>20.10111111111111</v>
-      </c>
-      <c r="D78" t="n">
+      <c r="E78" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
         <v>-25.4</v>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -66944,13 +67584,21 @@
       <c r="B79" t="n">
         <v>14.99</v>
       </c>
-      <c r="C79" t="n">
-        <v>20.32333333333333</v>
-      </c>
-      <c r="D79" t="n">
+      <c r="E79" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="F79" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
         <v>-26.2</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -66965,13 +67613,21 @@
       <c r="B80" t="n">
         <v>15.99</v>
       </c>
-      <c r="C80" t="n">
+      <c r="E80" t="n">
         <v>21.74</v>
       </c>
-      <c r="D80" t="n">
+      <c r="F80" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
         <v>-26.4</v>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -66986,13 +67642,21 @@
       <c r="B81" t="n">
         <v>14.24</v>
       </c>
-      <c r="C81" t="n">
-        <v>19.37944444444445</v>
-      </c>
-      <c r="D81" t="n">
+      <c r="E81" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="F81" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
         <v>-26.5</v>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -67007,13 +67671,21 @@
       <c r="B82" t="n">
         <v>14.99</v>
       </c>
-      <c r="C82" t="n">
-        <v>20.65666666666667</v>
-      </c>
-      <c r="D82" t="n">
+      <c r="E82" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="F82" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
         <v>-27.4</v>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -67028,13 +67700,21 @@
       <c r="B83" t="n">
         <v>3.49</v>
       </c>
-      <c r="C83" t="n">
-        <v>4.823888888888889</v>
-      </c>
-      <c r="D83" t="n">
+      <c r="E83" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
         <v>-27.7</v>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -67049,13 +67729,21 @@
       <c r="B84" t="n">
         <v>18.99</v>
       </c>
-      <c r="C84" t="n">
+      <c r="E84" t="n">
         <v>26.99</v>
       </c>
-      <c r="D84" t="n">
+      <c r="F84" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
         <v>-29.6</v>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -67070,13 +67758,21 @@
       <c r="B85" t="n">
         <v>4.49</v>
       </c>
-      <c r="C85" t="n">
-        <v>6.434444444444445</v>
-      </c>
-      <c r="D85" t="n">
+      <c r="E85" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="F85" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
         <v>-30.2</v>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -67091,13 +67787,21 @@
       <c r="B86" t="n">
         <v>18.99</v>
       </c>
-      <c r="C86" t="n">
-        <v>27.87888888888889</v>
-      </c>
-      <c r="D86" t="n">
+      <c r="E86" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="F86" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
         <v>-31.9</v>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -67112,13 +67816,21 @@
       <c r="B87" t="n">
         <v>9.99</v>
       </c>
-      <c r="C87" t="n">
-        <v>14.71222222222222</v>
-      </c>
-      <c r="D87" t="n">
+      <c r="E87" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="F87" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
         <v>-32.1</v>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -67133,13 +67845,21 @@
       <c r="B88" t="n">
         <v>4.49</v>
       </c>
-      <c r="C88" t="n">
-        <v>6.712222222222223</v>
-      </c>
-      <c r="D88" t="n">
+      <c r="E88" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="F88" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
         <v>-33.1</v>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -67154,13 +67874,21 @@
       <c r="B89" t="n">
         <v>12.49</v>
       </c>
-      <c r="C89" t="n">
-        <v>20.07333333333333</v>
-      </c>
-      <c r="D89" t="n">
+      <c r="E89" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="F89" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
         <v>-37.8</v>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
@@ -67175,20 +67903,28 @@
       <c r="B90" t="n">
         <v>3.49</v>
       </c>
-      <c r="C90" t="n">
-        <v>6.073333333333334</v>
-      </c>
-      <c r="D90" t="n">
+      <c r="E90" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="F90" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
         <v>-42.5</v>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>BELOW market (raise)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E90"/>
+  <autoFilter ref="A1:I90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
